--- a/ig/DM-37/CodeSystem-TRE-R356-ProfessionRessource.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R356-ProfessionRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="241">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -731,6 +731,12 @@
   </si>
   <si>
     <t>Réanimateur néonatologiste</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Conseiller conjugal et familial</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2261,6 +2267,18 @@
       </c>
       <c r="D96" s="2"/>
     </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="D97" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
